--- a/Översikt KROKOM.xlsx
+++ b/Översikt KROKOM.xlsx
@@ -601,7 +601,7 @@
         <v>45701</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
         <v>44522</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         <v>45995</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>45348</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>45950</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>45887</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1561,7 +1561,7 @@
         <v>46210</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
         <v>45384</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1851,7 +1851,7 @@
         <v>46000</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         <v>46198</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>46209</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>46119</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2403,7 +2403,7 @@
         <v>46055</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>45894</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         <v>45845</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2798,7 +2798,7 @@
         <v>45121</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>45630</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3060,7 +3060,7 @@
         <v>46000</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
         <v>46206</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3331,7 +3331,7 @@
         <v>45646</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3458,7 +3458,7 @@
         <v>44565</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3584,7 +3584,7 @@
         <v>45453</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         <v>45041</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3835,7 +3835,7 @@
         <v>45219</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3960,7 +3960,7 @@
         <v>45849</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4085,7 +4085,7 @@
         <v>44475</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4213,7 +4213,7 @@
         <v>45155</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4342,7 +4342,7 @@
         <v>45553</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4469,7 +4469,7 @@
         <v>45625</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4592,7 +4592,7 @@
         <v>46209</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>46044</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4847,7 +4847,7 @@
         <v>44575</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4973,7 +4973,7 @@
         <v>45663</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -5095,7 +5095,7 @@
         <v>45938</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5217,7 +5217,7 @@
         <v>45254</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5344,7 +5344,7 @@
         <v>45792</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5466,7 +5466,7 @@
         <v>45644</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5583,7 +5583,7 @@
         <v>45534</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5713,7 +5713,7 @@
         <v>45428</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5834,7 +5834,7 @@
         <v>44795</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5956,7 +5956,7 @@
         <v>45965</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -6077,7 +6077,7 @@
         <v>46055</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -6203,7 +6203,7 @@
         <v>45551</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6328,7 +6328,7 @@
         <v>46048</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6449,7 +6449,7 @@
         <v>46107</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6575,7 +6575,7 @@
         <v>45784</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6696,7 +6696,7 @@
         <v>44780</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6816,7 +6816,7 @@
         <v>44581</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6936,7 +6936,7 @@
         <v>45475</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         <v>46013</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -7185,7 +7185,7 @@
         <v>45734</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -7309,7 +7309,7 @@
         <v>44540</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7428,7 +7428,7 @@
         <v>46104</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7547,7 +7547,7 @@
         <v>46058</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7671,7 +7671,7 @@
         <v>45267</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7794,7 +7794,7 @@
         <v>45719</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7916,7 +7916,7 @@
         <v>45646</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -8034,7 +8034,7 @@
         <v>45646</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -8148,7 +8148,7 @@
         <v>45041</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -8266,7 +8266,7 @@
         <v>46114</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -8393,7 +8393,7 @@
         <v>46210</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8511,7 +8511,7 @@
         <v>46080</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         <v>46199</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8747,7 +8747,7 @@
         <v>46245</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         <v>44698</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8986,7 +8986,7 @@
         <v>44552</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -9108,7 +9108,7 @@
         <v>45639</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -9225,7 +9225,7 @@
         <v>45898</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -9342,7 +9342,7 @@
         <v>45457</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -9455,7 +9455,7 @@
         <v>46014</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9572,7 +9572,7 @@
         <v>45181</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9689,7 +9689,7 @@
         <v>45580</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9806,7 +9806,7 @@
         <v>46182</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9927,7 +9927,7 @@
         <v>45616</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -10045,7 +10045,7 @@
         <v>46052</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -10162,7 +10162,7 @@
         <v>44585</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -10283,7 +10283,7 @@
         <v>44714</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -10395,7 +10395,7 @@
         <v>45169</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -10516,7 +10516,7 @@
         <v>45219</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10632,7 +10632,7 @@
         <v>44540</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10744,7 +10744,7 @@
         <v>45149</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10860,7 +10860,7 @@
         <v>46042</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10976,7 +10976,7 @@
         <v>45943</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -11092,7 +11092,7 @@
         <v>46030</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -11208,7 +11208,7 @@
         <v>46244</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -11324,7 +11324,7 @@
         <v>44999</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -11441,7 +11441,7 @@
         <v>45180</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -11561,7 +11561,7 @@
         <v>45475</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11685,7 +11685,7 @@
         <v>46104</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11800,7 +11800,7 @@
         <v>45862</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11915,7 +11915,7 @@
         <v>46037</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -12030,7 +12030,7 @@
         <v>44904</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -12145,7 +12145,7 @@
         <v>46213</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -12260,7 +12260,7 @@
         <v>46233</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -12380,7 +12380,7 @@
         <v>46000</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -12500,7 +12500,7 @@
         <v>46258</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -12615,7 +12615,7 @@
         <v>45358</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12730,7 +12730,7 @@
         <v>44494</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12849,7 +12849,7 @@
         <v>44546</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12964,7 +12964,7 @@
         <v>45316</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -13078,7 +13078,7 @@
         <v>44834</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -13196,7 +13196,7 @@
         <v>45595</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -13306,7 +13306,7 @@
         <v>45869</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -13421,7 +13421,7 @@
         <v>44540</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -13531,7 +13531,7 @@
         <v>44557</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -13641,7 +13641,7 @@
         <v>46069</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -13751,7 +13751,7 @@
         <v>44540</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13861,7 +13861,7 @@
         <v>45755</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13975,7 +13975,7 @@
         <v>45877</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -14093,7 +14093,7 @@
         <v>45252</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -14208,7 +14208,7 @@
         <v>46209</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -14327,7 +14327,7 @@
         <v>44477</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -14442,7 +14442,7 @@
         <v>45268</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -14561,7 +14561,7 @@
         <v>46224</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -14675,7 +14675,7 @@
         <v>45862</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -14789,7 +14789,7 @@
         <v>46229</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -14903,7 +14903,7 @@
         <v>45944</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -15021,7 +15021,7 @@
         <v>46280</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -15131,7 +15131,7 @@
         <v>46006</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -15245,7 +15245,7 @@
         <v>44515</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -15359,7 +15359,7 @@
         <v>44534</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -15473,7 +15473,7 @@
         <v>44510</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -15586,7 +15586,7 @@
         <v>44553</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -15699,7 +15699,7 @@
         <v>45615</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -15817,7 +15817,7 @@
         <v>44631</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -15930,7 +15930,7 @@
         <v>45474</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -16048,7 +16048,7 @@
         <v>45959</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -16166,7 +16166,7 @@
         <v>44903</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -16284,7 +16284,7 @@
         <v>45370</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -16397,7 +16397,7 @@
         <v>46020</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -16510,7 +16510,7 @@
         <v>46209</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -16628,7 +16628,7 @@
         <v>46001</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -16741,7 +16741,7 @@
         <v>45432</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -16850,7 +16850,7 @@
         <v>46006</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -16963,7 +16963,7 @@
         <v>44540</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -17072,7 +17072,7 @@
         <v>46161</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -17185,7 +17185,7 @@
         <v>44873</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -17301,7 +17301,7 @@
         <v>45216</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -17418,7 +17418,7 @@
         <v>44895</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -17530,7 +17530,7 @@
         <v>44568</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -17642,7 +17642,7 @@
         <v>45121</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -17759,7 +17759,7 @@
         <v>45090</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -17867,7 +17867,7 @@
         <v>44879</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -17984,7 +17984,7 @@
         <v>45310</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -18092,7 +18092,7 @@
         <v>45169</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -18209,7 +18209,7 @@
         <v>45532</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -18321,7 +18321,7 @@
         <v>45643</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -18429,7 +18429,7 @@
         <v>45551</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -18545,7 +18545,7 @@
         <v>46191</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -18662,7 +18662,7 @@
         <v>46184</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -18774,7 +18774,7 @@
         <v>46196</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -18887,7 +18887,7 @@
         <v>45995</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -18999,7 +18999,7 @@
         <v>44757</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -19111,7 +19111,7 @@
         <v>46142</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -19224,7 +19224,7 @@
         <v>45967</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -19337,7 +19337,7 @@
         <v>46216</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -19449,7 +19449,7 @@
         <v>45800</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -19561,7 +19561,7 @@
         <v>46083</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -19673,7 +19673,7 @@
         <v>46206</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -19790,7 +19790,7 @@
         <v>45999</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -19902,7 +19902,7 @@
         <v>45560</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -20019,7 +20019,7 @@
         <v>45966</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -20131,7 +20131,7 @@
         <v>45715</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -20244,7 +20244,7 @@
         <v>46244</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -20356,7 +20356,7 @@
         <v>46276</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -20472,7 +20472,7 @@
         <v>46079</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -20589,7 +20589,7 @@
         <v>45300</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -20701,7 +20701,7 @@
         <v>45511</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -20809,7 +20809,7 @@
         <v>45764</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -20921,7 +20921,7 @@
         <v>46148</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -21033,7 +21033,7 @@
         <v>44757</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -21144,7 +21144,7 @@
         <v>44841</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -21255,7 +21255,7 @@
         <v>44966</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -21366,7 +21366,7 @@
         <v>45511</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -21477,7 +21477,7 @@
         <v>45547</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -21588,7 +21588,7 @@
         <v>45313</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -21699,7 +21699,7 @@
         <v>45233</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -21806,7 +21806,7 @@
         <v>44873</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -21921,7 +21921,7 @@
         <v>45635</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -22028,7 +22028,7 @@
         <v>45300</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -22139,7 +22139,7 @@
         <v>46195</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -22246,7 +22246,7 @@
         <v>46195</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -22357,7 +22357,7 @@
         <v>46196</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -22469,7 +22469,7 @@
         <v>45692</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -22581,7 +22581,7 @@
         <v>46001</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -22692,7 +22692,7 @@
         <v>46202</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -22812,7 +22812,7 @@
         <v>46020</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -22923,7 +22923,7 @@
         <v>46253</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -23034,7 +23034,7 @@
         <v>46030</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -23145,7 +23145,7 @@
         <v>46064</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -23256,7 +23256,7 @@
         <v>46274</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -23372,7 +23372,7 @@
         <v>45527</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -23488,7 +23488,7 @@
         <v>45624</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -23599,7 +23599,7 @@
         <v>46239</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -23715,7 +23715,7 @@
         <v>46245</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -23826,7 +23826,7 @@
         <v>45863</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -23942,7 +23942,7 @@
         <v>44546</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -24058,7 +24058,7 @@
         <v>45734</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -24169,7 +24169,7 @@
         <v>44797</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -24279,7 +24279,7 @@
         <v>45119</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -24389,7 +24389,7 @@
         <v>44568</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -24499,7 +24499,7 @@
         <v>44683</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -24605,7 +24605,7 @@
         <v>44867</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -24715,7 +24715,7 @@
         <v>45643</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -24821,7 +24821,7 @@
         <v>45348</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -24931,7 +24931,7 @@
         <v>45656</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -25046,7 +25046,7 @@
         <v>44568</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -25156,7 +25156,7 @@
         <v>45897</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -25262,7 +25262,7 @@
         <v>44879</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -25368,7 +25368,7 @@
         <v>45862</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -25474,7 +25474,7 @@
         <v>45376</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -25585,7 +25585,7 @@
         <v>45838</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -25691,7 +25691,7 @@
         <v>45975</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -25802,7 +25802,7 @@
         <v>45526</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -25912,7 +25912,7 @@
         <v>44797</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -26018,7 +26018,7 @@
         <v>45989</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -26124,7 +26124,7 @@
         <v>45603</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -26235,7 +26235,7 @@
         <v>46014</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -26345,7 +26345,7 @@
         <v>46035</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -26451,7 +26451,7 @@
         <v>45253</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -26561,7 +26561,7 @@
         <v>44757</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -26671,7 +26671,7 @@
         <v>44728</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -26786,7 +26786,7 @@
         <v>45748</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -26892,7 +26892,7 @@
         <v>46020</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -27002,7 +27002,7 @@
         <v>46149</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -27112,7 +27112,7 @@
         <v>46097</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -27222,7 +27222,7 @@
         <v>45981</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -27332,7 +27332,7 @@
         <v>45863</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -27447,7 +27447,7 @@
         <v>46042</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -27557,7 +27557,7 @@
         <v>46124</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -27668,7 +27668,7 @@
         <v>45418</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -27774,7 +27774,7 @@
         <v>45223</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -27889,7 +27889,7 @@
         <v>46247</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -27999,7 +27999,7 @@
         <v>46251</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -28105,7 +28105,7 @@
         <v>45216</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -28215,7 +28215,7 @@
         <v>45967</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -28326,7 +28326,7 @@
         <v>45630</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -28436,7 +28436,7 @@
         <v>46079</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -28551,7 +28551,7 @@
         <v>46132</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         <v>45554</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -28776,7 +28776,7 @@
         <v>46237</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -28886,7 +28886,7 @@
         <v>45453</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -28996,7 +28996,7 @@
         <v>45376</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -29111,7 +29111,7 @@
         <v>45376</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -29217,7 +29217,7 @@
         <v>44512</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -29327,7 +29327,7 @@
         <v>44512</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -29437,7 +29437,7 @@
         <v>44502</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -29551,7 +29551,7 @@
         <v>44512</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -29661,7 +29661,7 @@
         <v>44728</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -29771,7 +29771,7 @@
         <v>44742</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -29881,7 +29881,7 @@
         <v>45279</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -29986,7 +29986,7 @@
         <v>45098</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -30096,7 +30096,7 @@
         <v>45289</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -30205,7 +30205,7 @@
         <v>45670</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -30310,7 +30310,7 @@
         <v>45231</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -30420,7 +30420,7 @@
         <v>45751</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -30530,7 +30530,7 @@
         <v>45180</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -30644,7 +30644,7 @@
         <v>44630</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -30753,7 +30753,7 @@
         <v>45750</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -30858,7 +30858,7 @@
         <v>45839</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -30963,7 +30963,7 @@
         <v>45700</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -31072,7 +31072,7 @@
         <v>45407</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -31177,7 +31177,7 @@
         <v>45702</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -31287,7 +31287,7 @@
         <v>45931</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -31397,7 +31397,7 @@
         <v>45595</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -31506,7 +31506,7 @@
         <v>45595</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -31611,7 +31611,7 @@
         <v>45609</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -31720,7 +31720,7 @@
         <v>44847</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -31829,7 +31829,7 @@
         <v>45243</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -31934,7 +31934,7 @@
         <v>46161</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -32039,7 +32039,7 @@
         <v>45467</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -32148,7 +32148,7 @@
         <v>45994</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -32257,7 +32257,7 @@
         <v>45182</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -32362,7 +32362,7 @@
         <v>46048</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -32467,7 +32467,7 @@
         <v>45271</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -32572,7 +32572,7 @@
         <v>44847</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         <v>45595</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -32790,7 +32790,7 @@
         <v>46045</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -32900,7 +32900,7 @@
         <v>46176</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -33009,7 +33009,7 @@
         <v>44795</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -33123,7 +33123,7 @@
         <v>46189</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -33233,7 +33233,7 @@
         <v>46190</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -33338,7 +33338,7 @@
         <v>45647</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -33452,7 +33452,7 @@
         <v>46197</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -33557,7 +33557,7 @@
         <v>46199</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -33667,7 +33667,7 @@
         <v>45705</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -33777,7 +33777,7 @@
         <v>46030</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -33882,7 +33882,7 @@
         <v>46121</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -33992,7 +33992,7 @@
         <v>46199</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -34102,7 +34102,7 @@
         <v>45819</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -34207,7 +34207,7 @@
         <v>45153</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -34321,7 +34321,7 @@
         <v>44603</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -34426,7 +34426,7 @@
         <v>45595</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -34535,7 +34535,7 @@
         <v>46210</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -34645,7 +34645,7 @@
         <v>46251</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -34750,7 +34750,7 @@
         <v>46262</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -34855,7 +34855,7 @@
         <v>45371</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -34960,7 +34960,7 @@
         <v>45695</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -35065,7 +35065,7 @@
         <v>46048</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -35170,7 +35170,7 @@
         <v>46079</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -35280,7 +35280,7 @@
         <v>46279</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -35385,7 +35385,7 @@
         <v>45789</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -35490,7 +35490,7 @@
         <v>45079</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -35599,7 +35599,7 @@
         <v>46239</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -35709,7 +35709,7 @@
         <v>45645</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -35818,7 +35818,7 @@
         <v>45826</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -35923,7 +35923,7 @@
         <v>44263</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -36028,7 +36028,7 @@
         <v>44516</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -36142,7 +36142,7 @@
         <v>45327</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -36247,7 +36247,7 @@
         <v>45434</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -36356,7 +36356,7 @@
         <v>45366</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -36461,7 +36461,7 @@
         <v>45791</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -36571,7 +36571,7 @@
         <v>46111</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -36681,7 +36681,7 @@
         <v>44748</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -36759,7 +36759,7 @@
         <v>44473</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -36832,7 +36832,7 @@
         <v>44679</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -36910,7 +36910,7 @@
         <v>44665</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -36983,7 +36983,7 @@
         <v>44610</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -37056,7 +37056,7 @@
         <v>44494</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -37129,7 +37129,7 @@
         <v>44788</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -37202,7 +37202,7 @@
         <v>44524</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -37275,7 +37275,7 @@
         <v>44591</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -37348,7 +37348,7 @@
         <v>44577</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -37421,7 +37421,7 @@
         <v>44749</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -37494,7 +37494,7 @@
         <v>44831</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -37572,7 +37572,7 @@
         <v>44512</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -37650,7 +37650,7 @@
         <v>44502</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -37723,7 +37723,7 @@
         <v>44851</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -37801,7 +37801,7 @@
         <v>44466</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -37874,7 +37874,7 @@
         <v>44539</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -37947,7 +37947,7 @@
         <v>44495</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -38020,7 +38020,7 @@
         <v>44495</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -38093,7 +38093,7 @@
         <v>44502</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -38171,7 +38171,7 @@
         <v>44693</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -38244,7 +38244,7 @@
         <v>44473</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -38317,7 +38317,7 @@
         <v>44459</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -38390,7 +38390,7 @@
         <v>44848</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -38463,7 +38463,7 @@
         <v>44727</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -38536,7 +38536,7 @@
         <v>44848</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -38609,7 +38609,7 @@
         <v>44858</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -38682,7 +38682,7 @@
         <v>44524</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -38755,7 +38755,7 @@
         <v>44473</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -38828,7 +38828,7 @@
         <v>44459</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -38901,7 +38901,7 @@
         <v>44820</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -38974,7 +38974,7 @@
         <v>44519</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -39047,7 +39047,7 @@
         <v>44470</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -39120,7 +39120,7 @@
         <v>44526</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -39193,7 +39193,7 @@
         <v>44610</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -39266,7 +39266,7 @@
         <v>44697</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -39339,7 +39339,7 @@
         <v>44705</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -39412,7 +39412,7 @@
         <v>44468</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -39490,7 +39490,7 @@
         <v>45706</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -39563,7 +39563,7 @@
         <v>45460</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -39636,7 +39636,7 @@
         <v>45618</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -39709,7 +39709,7 @@
         <v>45022</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -39782,7 +39782,7 @@
         <v>45692</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -39855,7 +39855,7 @@
         <v>45457</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -39928,7 +39928,7 @@
         <v>45246</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -40001,7 +40001,7 @@
         <v>45726</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -40074,7 +40074,7 @@
         <v>44873</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -40147,7 +40147,7 @@
         <v>45190</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -40220,7 +40220,7 @@
         <v>44875</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -40293,7 +40293,7 @@
         <v>45107</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -40366,7 +40366,7 @@
         <v>45411</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -40444,7 +40444,7 @@
         <v>45392</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -40522,7 +40522,7 @@
         <v>45510</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -40600,7 +40600,7 @@
         <v>44911</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -40673,7 +40673,7 @@
         <v>44875</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -40746,7 +40746,7 @@
         <v>45457</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -40819,7 +40819,7 @@
         <v>45216</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -40892,7 +40892,7 @@
         <v>45701</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -40965,7 +40965,7 @@
         <v>44866</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -41038,7 +41038,7 @@
         <v>45719</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -41116,7 +41116,7 @@
         <v>44732</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -41189,7 +41189,7 @@
         <v>45203</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -41262,7 +41262,7 @@
         <v>44524</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -41335,7 +41335,7 @@
         <v>45090</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -41408,7 +41408,7 @@
         <v>44874</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -41481,7 +41481,7 @@
         <v>45343</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -41559,7 +41559,7 @@
         <v>45748</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -41632,7 +41632,7 @@
         <v>45414</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -41705,7 +41705,7 @@
         <v>45247</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -41778,7 +41778,7 @@
         <v>45180</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -41856,7 +41856,7 @@
         <v>44480</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -41929,7 +41929,7 @@
         <v>44887</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -42007,7 +42007,7 @@
         <v>45762</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -42085,7 +42085,7 @@
         <v>45757</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -42158,7 +42158,7 @@
         <v>45692</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -42236,7 +42236,7 @@
         <v>45232</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -42309,7 +42309,7 @@
         <v>45165</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -42382,7 +42382,7 @@
         <v>44855</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -42455,7 +42455,7 @@
         <v>44855</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -42528,7 +42528,7 @@
         <v>45204</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -42601,7 +42601,7 @@
         <v>45117</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -42674,7 +42674,7 @@
         <v>45638</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -42747,7 +42747,7 @@
         <v>45371</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -42820,7 +42820,7 @@
         <v>45250</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -42898,7 +42898,7 @@
         <v>45602</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -42971,7 +42971,7 @@
         <v>45140</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -43044,7 +43044,7 @@
         <v>45243</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -43117,7 +43117,7 @@
         <v>45203</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -43190,7 +43190,7 @@
         <v>45260</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -43263,7 +43263,7 @@
         <v>45117</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -43341,7 +43341,7 @@
         <v>45117</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -43419,7 +43419,7 @@
         <v>44757</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -43497,7 +43497,7 @@
         <v>45245</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -43575,7 +43575,7 @@
         <v>45649</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -43648,7 +43648,7 @@
         <v>45686</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -43726,7 +43726,7 @@
         <v>45475</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -43799,7 +43799,7 @@
         <v>45160</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -43877,7 +43877,7 @@
         <v>45721</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -43950,7 +43950,7 @@
         <v>45694</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -44028,7 +44028,7 @@
         <v>44498</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -44101,7 +44101,7 @@
         <v>45758</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -44174,7 +44174,7 @@
         <v>44658</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -44247,7 +44247,7 @@
         <v>45274</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -44320,7 +44320,7 @@
         <v>45257</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -44393,7 +44393,7 @@
         <v>45245</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -44466,7 +44466,7 @@
         <v>45180</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -44544,7 +44544,7 @@
         <v>45176</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -44622,7 +44622,7 @@
         <v>45190</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -44695,7 +44695,7 @@
         <v>44757</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -44773,7 +44773,7 @@
         <v>45471</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -44846,7 +44846,7 @@
         <v>45180</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -44924,7 +44924,7 @@
         <v>45245</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -45002,7 +45002,7 @@
         <v>44901</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -45080,7 +45080,7 @@
         <v>45099</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -45153,7 +45153,7 @@
         <v>45109</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -45231,7 +45231,7 @@
         <v>45694</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -45309,7 +45309,7 @@
         <v>45746</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -45382,7 +45382,7 @@
         <v>45719</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -45455,7 +45455,7 @@
         <v>45373</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -45528,7 +45528,7 @@
         <v>45097</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -45606,7 +45606,7 @@
         <v>45398</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -45679,7 +45679,7 @@
         <v>45216</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -45752,7 +45752,7 @@
         <v>44600</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -45825,7 +45825,7 @@
         <v>44788</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -45898,7 +45898,7 @@
         <v>45666</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -45971,7 +45971,7 @@
         <v>44522</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -46044,7 +46044,7 @@
         <v>45700</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -46117,7 +46117,7 @@
         <v>45686</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -46190,7 +46190,7 @@
         <v>45216</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -46263,7 +46263,7 @@
         <v>45747</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -46341,7 +46341,7 @@
         <v>45036</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -46414,7 +46414,7 @@
         <v>45036</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -46487,7 +46487,7 @@
         <v>45082</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -46565,7 +46565,7 @@
         <v>44938</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -46638,7 +46638,7 @@
         <v>44965</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -46716,7 +46716,7 @@
         <v>45987</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -46789,7 +46789,7 @@
         <v>45696</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -46862,7 +46862,7 @@
         <v>45217</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -46935,7 +46935,7 @@
         <v>45698</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -47008,7 +47008,7 @@
         <v>45342</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -47086,7 +47086,7 @@
         <v>45554</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -47164,7 +47164,7 @@
         <v>44592</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -47237,7 +47237,7 @@
         <v>45097</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -47310,7 +47310,7 @@
         <v>45607</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -47383,7 +47383,7 @@
         <v>45572</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -47461,7 +47461,7 @@
         <v>44741</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -47534,7 +47534,7 @@
         <v>45401</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -47607,7 +47607,7 @@
         <v>45889</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -47685,7 +47685,7 @@
         <v>45713</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -47763,7 +47763,7 @@
         <v>44544</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -47836,7 +47836,7 @@
         <v>45035</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -47909,7 +47909,7 @@
         <v>45378</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -47982,7 +47982,7 @@
         <v>45566</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -48055,7 +48055,7 @@
         <v>45133</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -48128,7 +48128,7 @@
         <v>44550</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -48201,7 +48201,7 @@
         <v>45453</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -48279,7 +48279,7 @@
         <v>45203</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -48352,7 +48352,7 @@
         <v>45706</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -48430,7 +48430,7 @@
         <v>45750</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -48508,7 +48508,7 @@
         <v>46138</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -48581,7 +48581,7 @@
         <v>45905</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -48654,7 +48654,7 @@
         <v>45905</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -48727,7 +48727,7 @@
         <v>46019</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -48800,7 +48800,7 @@
         <v>45776</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -48873,7 +48873,7 @@
         <v>45634</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -48946,7 +48946,7 @@
         <v>45594</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -49019,7 +49019,7 @@
         <v>45620</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -49092,7 +49092,7 @@
         <v>44974</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -49170,7 +49170,7 @@
         <v>45700</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -49248,7 +49248,7 @@
         <v>46058</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -49321,7 +49321,7 @@
         <v>45552</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -49394,7 +49394,7 @@
         <v>45635</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -49467,7 +49467,7 @@
         <v>44825</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -49540,7 +49540,7 @@
         <v>45966</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -49613,7 +49613,7 @@
         <v>45377</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -49686,7 +49686,7 @@
         <v>45203</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -49759,7 +49759,7 @@
         <v>46029</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -49832,7 +49832,7 @@
         <v>45453</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -49905,7 +49905,7 @@
         <v>45922</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -49978,7 +49978,7 @@
         <v>45922</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -50051,7 +50051,7 @@
         <v>44504</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -50124,7 +50124,7 @@
         <v>45415</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -50197,7 +50197,7 @@
         <v>45925</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -50270,7 +50270,7 @@
         <v>46069</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -50343,7 +50343,7 @@
         <v>45926</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -50421,7 +50421,7 @@
         <v>46142</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -50494,7 +50494,7 @@
         <v>44970</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -50567,7 +50567,7 @@
         <v>45930</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -50645,7 +50645,7 @@
         <v>45226</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -50718,7 +50718,7 @@
         <v>46142</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -50791,7 +50791,7 @@
         <v>46142</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -50864,7 +50864,7 @@
         <v>45407</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -50937,7 +50937,7 @@
         <v>45393</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -51010,7 +51010,7 @@
         <v>44970</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -51083,7 +51083,7 @@
         <v>45930</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -51161,7 +51161,7 @@
         <v>45547</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -51234,7 +51234,7 @@
         <v>45370</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -51307,7 +51307,7 @@
         <v>45469</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -51380,7 +51380,7 @@
         <v>45602</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -51453,7 +51453,7 @@
         <v>45933</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -51526,7 +51526,7 @@
         <v>45244</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -51599,7 +51599,7 @@
         <v>45676</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -51672,7 +51672,7 @@
         <v>45446</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -51750,7 +51750,7 @@
         <v>45931</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -51823,7 +51823,7 @@
         <v>45933</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -51896,7 +51896,7 @@
         <v>45639</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -51969,7 +51969,7 @@
         <v>45649</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -52042,7 +52042,7 @@
         <v>45324</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -52115,7 +52115,7 @@
         <v>45937</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -52188,7 +52188,7 @@
         <v>45744</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -52261,7 +52261,7 @@
         <v>44849</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -52334,7 +52334,7 @@
         <v>46147</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -52407,7 +52407,7 @@
         <v>45939</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -52480,7 +52480,7 @@
         <v>45538</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -52553,7 +52553,7 @@
         <v>45750</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -52626,7 +52626,7 @@
         <v>45560</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -52699,7 +52699,7 @@
         <v>45772</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -52772,7 +52772,7 @@
         <v>45772</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -52845,7 +52845,7 @@
         <v>45055</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -52918,7 +52918,7 @@
         <v>45945</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -52991,7 +52991,7 @@
         <v>45833</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -53069,7 +53069,7 @@
         <v>45924</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -53147,7 +53147,7 @@
         <v>45924</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -53225,7 +53225,7 @@
         <v>45608</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -53298,7 +53298,7 @@
         <v>45925</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -53376,7 +53376,7 @@
         <v>46070</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -53454,7 +53454,7 @@
         <v>45946</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -53532,7 +53532,7 @@
         <v>45721</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -53605,7 +53605,7 @@
         <v>45758</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -53683,7 +53683,7 @@
         <v>45950</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -53756,7 +53756,7 @@
         <v>45579</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -53829,7 +53829,7 @@
         <v>45950</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -53902,7 +53902,7 @@
         <v>45950</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -53975,7 +53975,7 @@
         <v>45674</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -54048,7 +54048,7 @@
         <v>45953</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -54121,7 +54121,7 @@
         <v>45042</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -54194,7 +54194,7 @@
         <v>45953</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -54267,7 +54267,7 @@
         <v>45953</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -54340,7 +54340,7 @@
         <v>44908</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -54418,7 +54418,7 @@
         <v>45467</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -54491,7 +54491,7 @@
         <v>45954</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -54569,7 +54569,7 @@
         <v>45935</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -54642,7 +54642,7 @@
         <v>45887</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -54715,7 +54715,7 @@
         <v>45412</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -54788,7 +54788,7 @@
         <v>46150</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -54861,7 +54861,7 @@
         <v>44686</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -54934,7 +54934,7 @@
         <v>45961</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -55007,7 +55007,7 @@
         <v>45265</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -55080,7 +55080,7 @@
         <v>45713</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -55158,7 +55158,7 @@
         <v>45649</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -55231,7 +55231,7 @@
         <v>45967</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -55309,7 +55309,7 @@
         <v>45966</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -55382,7 +55382,7 @@
         <v>44732</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -55455,7 +55455,7 @@
         <v>45967</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -55533,7 +55533,7 @@
         <v>45967</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -55611,7 +55611,7 @@
         <v>45165</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -55684,7 +55684,7 @@
         <v>45971</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -55757,7 +55757,7 @@
         <v>45600</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -55830,7 +55830,7 @@
         <v>45758</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -55903,7 +55903,7 @@
         <v>44557</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -55976,7 +55976,7 @@
         <v>44726</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -56049,7 +56049,7 @@
         <v>45975</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -56127,7 +56127,7 @@
         <v>45974</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -56200,7 +56200,7 @@
         <v>45975</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -56278,7 +56278,7 @@
         <v>45484</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -56356,7 +56356,7 @@
         <v>45484</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -56434,7 +56434,7 @@
         <v>45056</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -56507,7 +56507,7 @@
         <v>45979</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -56580,7 +56580,7 @@
         <v>44516</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -56653,7 +56653,7 @@
         <v>45467</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -56726,7 +56726,7 @@
         <v>45198</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -56804,7 +56804,7 @@
         <v>45982</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -56877,7 +56877,7 @@
         <v>45278</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -56950,7 +56950,7 @@
         <v>45694</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -57023,7 +57023,7 @@
         <v>45699</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -57101,7 +57101,7 @@
         <v>46161</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -57174,7 +57174,7 @@
         <v>44466</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -57247,7 +57247,7 @@
         <v>45309</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -57320,7 +57320,7 @@
         <v>46161</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -57393,7 +57393,7 @@
         <v>45989</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -57466,7 +57466,7 @@
         <v>45112</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -57539,7 +57539,7 @@
         <v>46161</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -57612,7 +57612,7 @@
         <v>46161</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -57685,7 +57685,7 @@
         <v>45989</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -57758,7 +57758,7 @@
         <v>45992</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -57831,7 +57831,7 @@
         <v>45672</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -57909,7 +57909,7 @@
         <v>46099</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -57982,7 +57982,7 @@
         <v>46161</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -58055,7 +58055,7 @@
         <v>46161</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -58128,7 +58128,7 @@
         <v>45749</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -58201,7 +58201,7 @@
         <v>45726</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -58279,7 +58279,7 @@
         <v>45226</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -58352,7 +58352,7 @@
         <v>45608</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -58425,7 +58425,7 @@
         <v>45527</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -58498,7 +58498,7 @@
         <v>45369</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -58571,7 +58571,7 @@
         <v>45714</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -58649,7 +58649,7 @@
         <v>45525</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -58722,7 +58722,7 @@
         <v>45583</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -58795,7 +58795,7 @@
         <v>45477</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -58873,7 +58873,7 @@
         <v>44726</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -58946,7 +58946,7 @@
         <v>45995</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -59019,7 +59019,7 @@
         <v>45994</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -59092,7 +59092,7 @@
         <v>44721</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -59170,7 +59170,7 @@
         <v>44922</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -59243,7 +59243,7 @@
         <v>45999</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -59321,7 +59321,7 @@
         <v>46000</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -59399,7 +59399,7 @@
         <v>46000</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -59472,7 +59472,7 @@
         <v>46000</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -59550,7 +59550,7 @@
         <v>46000</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -59623,7 +59623,7 @@
         <v>46000</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -59701,7 +59701,7 @@
         <v>46164</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -59774,7 +59774,7 @@
         <v>46000</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -59852,7 +59852,7 @@
         <v>45746</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -59930,7 +59930,7 @@
         <v>46000</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -60003,7 +60003,7 @@
         <v>46000</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -60076,7 +60076,7 @@
         <v>45411</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -60154,7 +60154,7 @@
         <v>44510</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -60227,7 +60227,7 @@
         <v>46002</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -60305,7 +60305,7 @@
         <v>46003</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -60378,7 +60378,7 @@
         <v>46164</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -60451,7 +60451,7 @@
         <v>46003</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -60529,7 +60529,7 @@
         <v>46007</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -60602,7 +60602,7 @@
         <v>46007</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -60675,7 +60675,7 @@
         <v>46005</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -60753,7 +60753,7 @@
         <v>46007</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -60826,7 +60826,7 @@
         <v>46007</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -60899,7 +60899,7 @@
         <v>46168</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -60977,7 +60977,7 @@
         <v>45204</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -61050,7 +61050,7 @@
         <v>44750</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -61123,7 +61123,7 @@
         <v>44904</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -61196,7 +61196,7 @@
         <v>45693</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -61269,7 +61269,7 @@
         <v>45000</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -61342,7 +61342,7 @@
         <v>45483</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -61415,7 +61415,7 @@
         <v>45701</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -61488,7 +61488,7 @@
         <v>45266</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -61561,7 +61561,7 @@
         <v>46168</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -61634,7 +61634,7 @@
         <v>46001</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -61707,7 +61707,7 @@
         <v>45796</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -61780,7 +61780,7 @@
         <v>46018</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -61853,7 +61853,7 @@
         <v>46020</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -61926,7 +61926,7 @@
         <v>45488</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -62004,7 +62004,7 @@
         <v>46024</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -62082,7 +62082,7 @@
         <v>45408</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -62155,7 +62155,7 @@
         <v>45282</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -62228,7 +62228,7 @@
         <v>44582</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -62301,7 +62301,7 @@
         <v>45145</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -62379,7 +62379,7 @@
         <v>45118</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -62452,7 +62452,7 @@
         <v>46030</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -62525,7 +62525,7 @@
         <v>46170</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -62598,7 +62598,7 @@
         <v>45656</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -62676,7 +62676,7 @@
         <v>46174</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -62749,7 +62749,7 @@
         <v>45595</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -62822,7 +62822,7 @@
         <v>45602</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -62895,7 +62895,7 @@
         <v>46174</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -62968,7 +62968,7 @@
         <v>45474</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -63041,7 +63041,7 @@
         <v>45601</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -63114,7 +63114,7 @@
         <v>46174</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -63187,7 +63187,7 @@
         <v>46037</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -63260,7 +63260,7 @@
         <v>44880</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -63333,7 +63333,7 @@
         <v>46041</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -63406,7 +63406,7 @@
         <v>45238</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -63479,7 +63479,7 @@
         <v>45943</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -63557,7 +63557,7 @@
         <v>45943</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -63635,7 +63635,7 @@
         <v>45960</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -63713,7 +63713,7 @@
         <v>45887</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -63791,7 +63791,7 @@
         <v>46043</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -63864,7 +63864,7 @@
         <v>45972</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -63942,7 +63942,7 @@
         <v>45986</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -64020,7 +64020,7 @@
         <v>46174</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -64093,7 +64093,7 @@
         <v>46120</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -64166,7 +64166,7 @@
         <v>45484</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -64244,7 +64244,7 @@
         <v>46045</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -64322,7 +64322,7 @@
         <v>45836</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -64400,7 +64400,7 @@
         <v>46045</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -64478,7 +64478,7 @@
         <v>46007</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -64551,7 +64551,7 @@
         <v>46044</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -64624,7 +64624,7 @@
         <v>46048</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -64697,7 +64697,7 @@
         <v>46048</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -64775,7 +64775,7 @@
         <v>45750</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -64848,7 +64848,7 @@
         <v>46048</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -64921,7 +64921,7 @@
         <v>46048</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -64994,7 +64994,7 @@
         <v>46153</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -65067,7 +65067,7 @@
         <v>45532</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -65140,7 +65140,7 @@
         <v>46048</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -65213,7 +65213,7 @@
         <v>46048</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -65286,7 +65286,7 @@
         <v>46048</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -65364,7 +65364,7 @@
         <v>45897</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -65437,7 +65437,7 @@
         <v>46047</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -65515,7 +65515,7 @@
         <v>46046</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -65593,7 +65593,7 @@
         <v>46048</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -65666,7 +65666,7 @@
         <v>46048</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -65739,7 +65739,7 @@
         <v>46048</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -65812,7 +65812,7 @@
         <v>46051</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -65885,7 +65885,7 @@
         <v>44714</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -65958,7 +65958,7 @@
         <v>45988</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -66031,7 +66031,7 @@
         <v>46051</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -66109,7 +66109,7 @@
         <v>44971</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -66182,7 +66182,7 @@
         <v>46051</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -66260,7 +66260,7 @@
         <v>44901</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -66338,7 +66338,7 @@
         <v>45877</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -66416,7 +66416,7 @@
         <v>45870</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -66489,7 +66489,7 @@
         <v>45466</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -66562,7 +66562,7 @@
         <v>45932</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -66640,7 +66640,7 @@
         <v>45954</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -66718,7 +66718,7 @@
         <v>46178</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -66796,7 +66796,7 @@
         <v>44939</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -66869,7 +66869,7 @@
         <v>45246</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -66942,7 +66942,7 @@
         <v>46000</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -67015,7 +67015,7 @@
         <v>46120</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -67088,7 +67088,7 @@
         <v>45720</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -67166,7 +67166,7 @@
         <v>45740</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -67244,7 +67244,7 @@
         <v>45726</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -67322,7 +67322,7 @@
         <v>45723</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -67395,7 +67395,7 @@
         <v>45733</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -67468,7 +67468,7 @@
         <v>45740</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -67546,7 +67546,7 @@
         <v>45607</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -67619,7 +67619,7 @@
         <v>46056</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -67692,7 +67692,7 @@
         <v>44498</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -67765,7 +67765,7 @@
         <v>46057</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -67838,7 +67838,7 @@
         <v>46057</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -67911,7 +67911,7 @@
         <v>44858</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -67984,7 +67984,7 @@
         <v>46180</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -68057,7 +68057,7 @@
         <v>45635</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -68130,7 +68130,7 @@
         <v>46058</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -68203,7 +68203,7 @@
         <v>46177</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -68281,7 +68281,7 @@
         <v>46062</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -68354,7 +68354,7 @@
         <v>46064</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -68427,7 +68427,7 @@
         <v>44865</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -68500,7 +68500,7 @@
         <v>45701</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -68573,7 +68573,7 @@
         <v>46069</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -68646,7 +68646,7 @@
         <v>44741</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -68719,7 +68719,7 @@
         <v>45615</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -68797,7 +68797,7 @@
         <v>46069</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -68870,7 +68870,7 @@
         <v>46070</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -68948,7 +68948,7 @@
         <v>46070</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -69026,7 +69026,7 @@
         <v>46071</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -69099,7 +69099,7 @@
         <v>45474</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -69172,7 +69172,7 @@
         <v>45173</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -69250,7 +69250,7 @@
         <v>45721</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -69323,7 +69323,7 @@
         <v>45560</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -69401,7 +69401,7 @@
         <v>45699</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -69479,7 +69479,7 @@
         <v>45700</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -69557,7 +69557,7 @@
         <v>45614</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -69630,7 +69630,7 @@
         <v>46184</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -69703,7 +69703,7 @@
         <v>45056</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -69776,7 +69776,7 @@
         <v>45499</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -69849,7 +69849,7 @@
         <v>46083</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -69922,7 +69922,7 @@
         <v>45152</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -70000,7 +70000,7 @@
         <v>46188</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -70078,7 +70078,7 @@
         <v>46085</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -70156,7 +70156,7 @@
         <v>45708</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -70234,7 +70234,7 @@
         <v>45708</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -70312,7 +70312,7 @@
         <v>46090</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -70385,7 +70385,7 @@
         <v>45139</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -70463,7 +70463,7 @@
         <v>46185</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -70536,7 +70536,7 @@
         <v>44961</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -70609,7 +70609,7 @@
         <v>45826</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -70687,7 +70687,7 @@
         <v>46090</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -70760,7 +70760,7 @@
         <v>46189</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -70838,7 +70838,7 @@
         <v>44764</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -70911,7 +70911,7 @@
         <v>44764</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -70984,7 +70984,7 @@
         <v>45195</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -71057,7 +71057,7 @@
         <v>46190</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -71130,7 +71130,7 @@
         <v>46129</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -71203,7 +71203,7 @@
         <v>44834</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -71281,7 +71281,7 @@
         <v>45448</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -71359,7 +71359,7 @@
         <v>45695</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -71437,7 +71437,7 @@
         <v>45930</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -71515,7 +71515,7 @@
         <v>45348</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -71588,7 +71588,7 @@
         <v>46191</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -71666,7 +71666,7 @@
         <v>46099</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -71739,7 +71739,7 @@
         <v>45700</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -71817,7 +71817,7 @@
         <v>46056</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -71890,7 +71890,7 @@
         <v>46104</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -71963,7 +71963,7 @@
         <v>46106</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -72036,7 +72036,7 @@
         <v>45560</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -72114,7 +72114,7 @@
         <v>46107</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -72192,7 +72192,7 @@
         <v>45740</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -72265,7 +72265,7 @@
         <v>46113</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -72343,7 +72343,7 @@
         <v>46111</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -72421,7 +72421,7 @@
         <v>45720</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -72494,7 +72494,7 @@
         <v>45055</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -72567,7 +72567,7 @@
         <v>46202</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -72645,7 +72645,7 @@
         <v>45602</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -72718,7 +72718,7 @@
         <v>45713</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -72796,7 +72796,7 @@
         <v>46117</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -72869,7 +72869,7 @@
         <v>45056</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -72942,7 +72942,7 @@
         <v>45182</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -73015,7 +73015,7 @@
         <v>45485</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -73088,7 +73088,7 @@
         <v>46202</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -73166,7 +73166,7 @@
         <v>45476</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -73239,7 +73239,7 @@
         <v>46122</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -73312,7 +73312,7 @@
         <v>46125</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -73385,7 +73385,7 @@
         <v>45362</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -73458,7 +73458,7 @@
         <v>46126</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -73531,7 +73531,7 @@
         <v>46124</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -73609,7 +73609,7 @@
         <v>46126</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -73682,7 +73682,7 @@
         <v>46126</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -73755,7 +73755,7 @@
         <v>45392</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -73833,7 +73833,7 @@
         <v>46124</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -73911,7 +73911,7 @@
         <v>45555</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -73984,7 +73984,7 @@
         <v>46202</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -74062,7 +74062,7 @@
         <v>45362</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -74135,7 +74135,7 @@
         <v>45401</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -74208,7 +74208,7 @@
         <v>46133</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -74286,7 +74286,7 @@
         <v>45580</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -74364,7 +74364,7 @@
         <v>44887</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -74442,7 +74442,7 @@
         <v>46133</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -74520,7 +74520,7 @@
         <v>45760</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -74593,7 +74593,7 @@
         <v>46132</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -74666,7 +74666,7 @@
         <v>44818</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -74739,7 +74739,7 @@
         <v>46135</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -74812,7 +74812,7 @@
         <v>46135</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -74885,7 +74885,7 @@
         <v>46134</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -74958,7 +74958,7 @@
         <v>45602</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -75031,7 +75031,7 @@
         <v>45452</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -75109,7 +75109,7 @@
         <v>45225</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -75182,7 +75182,7 @@
         <v>45643</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -75255,7 +75255,7 @@
         <v>44792</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -75328,7 +75328,7 @@
         <v>45257</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -75401,7 +75401,7 @@
         <v>45182</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -75474,7 +75474,7 @@
         <v>45168</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -75547,7 +75547,7 @@
         <v>45692</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -75620,7 +75620,7 @@
         <v>46204</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -75698,7 +75698,7 @@
         <v>44488</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -75771,7 +75771,7 @@
         <v>46246</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -75844,7 +75844,7 @@
         <v>45751</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -75922,7 +75922,7 @@
         <v>45477</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -76000,7 +76000,7 @@
         <v>45369</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -76073,7 +76073,7 @@
         <v>45243</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -76151,7 +76151,7 @@
         <v>45707</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -76229,7 +76229,7 @@
         <v>45744</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -76307,7 +76307,7 @@
         <v>46248</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -76380,7 +76380,7 @@
         <v>46206</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -76458,7 +76458,7 @@
         <v>46209</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -76536,7 +76536,7 @@
         <v>46253</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -76609,7 +76609,7 @@
         <v>46209</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -76687,7 +76687,7 @@
         <v>46209</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -76760,7 +76760,7 @@
         <v>45700</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -76833,7 +76833,7 @@
         <v>45700</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -76911,7 +76911,7 @@
         <v>45692</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -76984,7 +76984,7 @@
         <v>45635</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -77057,7 +77057,7 @@
         <v>46209</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -77135,7 +77135,7 @@
         <v>45593</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -77208,7 +77208,7 @@
         <v>44601</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -77281,7 +77281,7 @@
         <v>46253</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -77354,7 +77354,7 @@
         <v>45474</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -77427,7 +77427,7 @@
         <v>46211</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -77500,7 +77500,7 @@
         <v>44972</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -77573,7 +77573,7 @@
         <v>45189</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -77646,7 +77646,7 @@
         <v>45310</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -77719,7 +77719,7 @@
         <v>44803</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -77792,7 +77792,7 @@
         <v>45707</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -77870,7 +77870,7 @@
         <v>45090</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -77943,7 +77943,7 @@
         <v>44596</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -78016,7 +78016,7 @@
         <v>46048</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -78089,7 +78089,7 @@
         <v>46214</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -78167,7 +78167,7 @@
         <v>44715</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -78245,7 +78245,7 @@
         <v>46261</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -78318,7 +78318,7 @@
         <v>46265</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -78391,7 +78391,7 @@
         <v>46265</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -78464,7 +78464,7 @@
         <v>45226</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -78537,7 +78537,7 @@
         <v>46204</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -78615,7 +78615,7 @@
         <v>46265</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -78688,7 +78688,7 @@
         <v>45123</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -78766,7 +78766,7 @@
         <v>45602</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -78839,7 +78839,7 @@
         <v>46265</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -78912,7 +78912,7 @@
         <v>46265</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -78985,7 +78985,7 @@
         <v>46209</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -79058,7 +79058,7 @@
         <v>46233</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -79136,7 +79136,7 @@
         <v>46233</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -79214,7 +79214,7 @@
         <v>46233</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -79292,7 +79292,7 @@
         <v>45630</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -79365,7 +79365,7 @@
         <v>45189</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -79438,7 +79438,7 @@
         <v>45713</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -79516,7 +79516,7 @@
         <v>45693</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -79589,7 +79589,7 @@
         <v>45713</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -79667,7 +79667,7 @@
         <v>45386</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -79740,7 +79740,7 @@
         <v>45630</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -79813,7 +79813,7 @@
         <v>46162</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -79886,7 +79886,7 @@
         <v>45638</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -79959,7 +79959,7 @@
         <v>45452</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -80037,7 +80037,7 @@
         <v>45721</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -80110,7 +80110,7 @@
         <v>44483</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -80183,7 +80183,7 @@
         <v>45748</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -80261,7 +80261,7 @@
         <v>46225</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -80339,7 +80339,7 @@
         <v>46048</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -80412,7 +80412,7 @@
         <v>46229</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -80485,7 +80485,7 @@
         <v>46229</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -80558,7 +80558,7 @@
         <v>46229</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -80631,7 +80631,7 @@
         <v>46268</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -80704,7 +80704,7 @@
         <v>46211</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -80777,7 +80777,7 @@
         <v>45712</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -80850,7 +80850,7 @@
         <v>45715</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -80928,7 +80928,7 @@
         <v>45693</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -81001,7 +81001,7 @@
         <v>46149</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -81074,7 +81074,7 @@
         <v>46149</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -81147,7 +81147,7 @@
         <v>46211</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -81220,7 +81220,7 @@
         <v>45696</v>
       </c>
       <c r="E913" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
@@ -81298,7 +81298,7 @@
         <v>45786</v>
       </c>
       <c r="E914" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F914" t="inlineStr">
         <is>
@@ -81371,7 +81371,7 @@
         <v>45786</v>
       </c>
       <c r="E915" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F915" t="inlineStr">
         <is>
@@ -81444,7 +81444,7 @@
         <v>45918</v>
       </c>
       <c r="E916" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F916" t="inlineStr">
         <is>
@@ -81517,7 +81517,7 @@
         <v>46229</v>
       </c>
       <c r="E917" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F917" t="inlineStr">
         <is>
@@ -81590,7 +81590,7 @@
         <v>46229</v>
       </c>
       <c r="E918" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F918" t="inlineStr">
         <is>
@@ -81663,7 +81663,7 @@
         <v>45968</v>
       </c>
       <c r="E919" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F919" t="inlineStr">
         <is>
@@ -81736,7 +81736,7 @@
         <v>45911</v>
       </c>
       <c r="E920" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F920" t="inlineStr">
         <is>
@@ -81809,7 +81809,7 @@
         <v>45911</v>
       </c>
       <c r="E921" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F921" t="inlineStr">
         <is>
@@ -81882,7 +81882,7 @@
         <v>46149</v>
       </c>
       <c r="E922" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F922" t="inlineStr">
         <is>
@@ -81955,7 +81955,7 @@
         <v>45923</v>
       </c>
       <c r="E923" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F923" t="inlineStr">
         <is>
@@ -82028,7 +82028,7 @@
         <v>46113</v>
       </c>
       <c r="E924" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F924" t="inlineStr">
         <is>
@@ -82101,7 +82101,7 @@
         <v>46196</v>
       </c>
       <c r="E925" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F925" t="inlineStr">
         <is>
@@ -82179,7 +82179,7 @@
         <v>46233</v>
       </c>
       <c r="E926" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F926" t="inlineStr">
         <is>
@@ -82257,7 +82257,7 @@
         <v>46036</v>
       </c>
       <c r="E927" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F927" t="inlineStr">
         <is>
@@ -82330,7 +82330,7 @@
         <v>45785</v>
       </c>
       <c r="E928" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F928" t="inlineStr">
         <is>
@@ -82403,7 +82403,7 @@
         <v>46094</v>
       </c>
       <c r="E929" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F929" t="inlineStr">
         <is>
@@ -82476,7 +82476,7 @@
         <v>45713</v>
       </c>
       <c r="E930" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F930" t="inlineStr">
         <is>
@@ -82554,7 +82554,7 @@
         <v>46233</v>
       </c>
       <c r="E931" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F931" t="inlineStr">
         <is>
@@ -82632,7 +82632,7 @@
         <v>46233</v>
       </c>
       <c r="E932" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F932" t="inlineStr">
         <is>
@@ -82710,7 +82710,7 @@
         <v>46142</v>
       </c>
       <c r="E933" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F933" t="inlineStr">
         <is>
@@ -82788,7 +82788,7 @@
         <v>46107</v>
       </c>
       <c r="E934" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F934" t="inlineStr">
         <is>
@@ -82894,7 +82894,7 @@
         <v>46233</v>
       </c>
       <c r="E935" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F935" t="inlineStr">
         <is>
@@ -82967,7 +82967,7 @@
         <v>46274</v>
       </c>
       <c r="E936" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F936" t="inlineStr">
         <is>
@@ -83045,7 +83045,7 @@
         <v>45786</v>
       </c>
       <c r="E937" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F937" t="inlineStr">
         <is>
@@ -83118,7 +83118,7 @@
         <v>46043</v>
       </c>
       <c r="E938" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F938" t="inlineStr">
         <is>
@@ -83191,7 +83191,7 @@
         <v>46155</v>
       </c>
       <c r="E939" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F939" t="inlineStr">
         <is>
@@ -83264,7 +83264,7 @@
         <v>46205</v>
       </c>
       <c r="E940" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F940" t="inlineStr">
         <is>
@@ -83337,7 +83337,7 @@
         <v>46127</v>
       </c>
       <c r="E941" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F941" t="inlineStr">
         <is>
@@ -83410,7 +83410,7 @@
         <v>46280</v>
       </c>
       <c r="E942" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F942" t="inlineStr">
         <is>
@@ -83483,7 +83483,7 @@
         <v>46279</v>
       </c>
       <c r="E943" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F943" t="inlineStr">
         <is>
@@ -83556,7 +83556,7 @@
         <v>46237</v>
       </c>
       <c r="E944" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F944" t="inlineStr">
         <is>
@@ -83634,7 +83634,7 @@
         <v>46237</v>
       </c>
       <c r="E945" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F945" t="inlineStr">
         <is>
@@ -83712,7 +83712,7 @@
         <v>45786</v>
       </c>
       <c r="E946" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F946" t="inlineStr">
         <is>
@@ -83785,7 +83785,7 @@
         <v>46281</v>
       </c>
       <c r="E947" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F947" t="inlineStr">
         <is>
@@ -83863,7 +83863,7 @@
         <v>46237</v>
       </c>
       <c r="E948" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F948" t="inlineStr">
         <is>
@@ -83941,7 +83941,7 @@
         <v>46279</v>
       </c>
       <c r="E949" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F949" t="inlineStr">
         <is>
@@ -84014,7 +84014,7 @@
         <v>46281</v>
       </c>
       <c r="E950" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F950" t="inlineStr">
         <is>
@@ -84092,7 +84092,7 @@
         <v>45632</v>
       </c>
       <c r="E951" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F951" t="inlineStr">
         <is>
@@ -84165,7 +84165,7 @@
         <v>46237</v>
       </c>
       <c r="E952" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F952" t="inlineStr">
         <is>
@@ -84238,7 +84238,7 @@
         <v>46279</v>
       </c>
       <c r="E953" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F953" t="inlineStr">
         <is>
@@ -84311,7 +84311,7 @@
         <v>45195</v>
       </c>
       <c r="E954" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F954" t="inlineStr">
         <is>
@@ -84389,7 +84389,7 @@
         <v>45791</v>
       </c>
       <c r="E955" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F955" t="inlineStr">
         <is>
@@ -84462,7 +84462,7 @@
         <v>45631</v>
       </c>
       <c r="E956" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F956" t="inlineStr">
         <is>
@@ -84535,7 +84535,7 @@
         <v>45791</v>
       </c>
       <c r="E957" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F957" t="inlineStr">
         <is>
@@ -84608,7 +84608,7 @@
         <v>45695</v>
       </c>
       <c r="E958" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F958" t="inlineStr">
         <is>
@@ -84686,7 +84686,7 @@
         <v>46237</v>
       </c>
       <c r="E959" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F959" t="inlineStr">
         <is>
@@ -84759,7 +84759,7 @@
         <v>46239</v>
       </c>
       <c r="E960" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F960" t="inlineStr">
         <is>
@@ -84832,7 +84832,7 @@
         <v>45166</v>
       </c>
       <c r="E961" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F961" t="inlineStr">
         <is>
@@ -84905,7 +84905,7 @@
         <v>46280</v>
       </c>
       <c r="E962" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F962" t="inlineStr">
         <is>
@@ -84978,7 +84978,7 @@
         <v>46237</v>
       </c>
       <c r="E963" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F963" t="inlineStr">
         <is>
@@ -85056,7 +85056,7 @@
         <v>46237</v>
       </c>
       <c r="E964" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F964" t="inlineStr">
         <is>
@@ -85134,7 +85134,7 @@
         <v>45662</v>
       </c>
       <c r="E965" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F965" t="inlineStr">
         <is>
@@ -85207,7 +85207,7 @@
         <v>46240</v>
       </c>
       <c r="E966" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F966" t="inlineStr">
         <is>
@@ -85285,7 +85285,7 @@
         <v>45698</v>
       </c>
       <c r="E967" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F967" t="inlineStr">
         <is>
@@ -85358,7 +85358,7 @@
         <v>45695</v>
       </c>
       <c r="E968" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F968" t="inlineStr">
         <is>
@@ -85436,7 +85436,7 @@
         <v>46239</v>
       </c>
       <c r="E969" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F969" t="inlineStr">
         <is>
@@ -85514,7 +85514,7 @@
         <v>45833</v>
       </c>
       <c r="E970" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F970" t="inlineStr">
         <is>
@@ -85587,7 +85587,7 @@
         <v>45706</v>
       </c>
       <c r="E971" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F971" t="inlineStr">
         <is>
@@ -85660,7 +85660,7 @@
         <v>46274</v>
       </c>
       <c r="E972" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F972" t="inlineStr">
         <is>
@@ -85733,7 +85733,7 @@
         <v>45378</v>
       </c>
       <c r="E973" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F973" t="inlineStr">
         <is>
@@ -85806,7 +85806,7 @@
         <v>46239</v>
       </c>
       <c r="E974" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F974" t="inlineStr">
         <is>
@@ -85884,7 +85884,7 @@
         <v>45791</v>
       </c>
       <c r="E975" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F975" t="inlineStr">
         <is>
@@ -85957,7 +85957,7 @@
         <v>46274</v>
       </c>
       <c r="E976" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F976" t="inlineStr">
         <is>
@@ -86035,7 +86035,7 @@
         <v>46276</v>
       </c>
       <c r="E977" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F977" t="inlineStr">
         <is>
@@ -86113,7 +86113,7 @@
         <v>46240</v>
       </c>
       <c r="E978" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F978" t="inlineStr">
         <is>
@@ -86186,7 +86186,7 @@
         <v>46239</v>
       </c>
       <c r="E979" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F979" t="inlineStr">
         <is>
@@ -86264,7 +86264,7 @@
         <v>45833</v>
       </c>
       <c r="E980" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F980" t="inlineStr">
         <is>
@@ -86337,7 +86337,7 @@
         <v>46240</v>
       </c>
       <c r="E981" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F981" t="inlineStr">
         <is>
@@ -86415,7 +86415,7 @@
         <v>45719</v>
       </c>
       <c r="E982" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F982" t="inlineStr">
         <is>
@@ -86488,7 +86488,7 @@
         <v>45684</v>
       </c>
       <c r="E983" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F983" t="inlineStr">
         <is>
@@ -86566,7 +86566,7 @@
         <v>45746</v>
       </c>
       <c r="E984" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F984" t="inlineStr">
         <is>
@@ -86644,7 +86644,7 @@
         <v>46239</v>
       </c>
       <c r="E985" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F985" t="inlineStr">
         <is>
@@ -86722,7 +86722,7 @@
         <v>46240</v>
       </c>
       <c r="E986" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F986" t="inlineStr">
         <is>
@@ -86800,7 +86800,7 @@
         <v>45803</v>
       </c>
       <c r="E987" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F987" t="inlineStr">
         <is>
@@ -86873,7 +86873,7 @@
         <v>45800</v>
       </c>
       <c r="E988" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F988" t="inlineStr">
         <is>
@@ -86946,7 +86946,7 @@
         <v>45833</v>
       </c>
       <c r="E989" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F989" t="inlineStr">
         <is>
@@ -87019,7 +87019,7 @@
         <v>45764</v>
       </c>
       <c r="E990" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F990" t="inlineStr">
         <is>
@@ -87092,7 +87092,7 @@
         <v>45692</v>
       </c>
       <c r="E991" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F991" t="inlineStr">
         <is>
@@ -87170,7 +87170,7 @@
         <v>45687</v>
       </c>
       <c r="E992" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F992" t="inlineStr">
         <is>
@@ -87248,7 +87248,7 @@
         <v>45695</v>
       </c>
       <c r="E993" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F993" t="inlineStr">
         <is>
@@ -87326,7 +87326,7 @@
         <v>45805</v>
       </c>
       <c r="E994" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F994" t="inlineStr">
         <is>
@@ -87399,7 +87399,7 @@
         <v>45807</v>
       </c>
       <c r="E995" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F995" t="inlineStr">
         <is>
@@ -87472,7 +87472,7 @@
         <v>45751</v>
       </c>
       <c r="E996" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F996" t="inlineStr">
         <is>
@@ -87545,7 +87545,7 @@
         <v>45751</v>
       </c>
       <c r="E997" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F997" t="inlineStr">
         <is>
@@ -87618,7 +87618,7 @@
         <v>45261</v>
       </c>
       <c r="E998" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F998" t="inlineStr">
         <is>
@@ -87691,7 +87691,7 @@
         <v>45737</v>
       </c>
       <c r="E999" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F999" t="inlineStr">
         <is>
@@ -87764,7 +87764,7 @@
         <v>45811</v>
       </c>
       <c r="E1000" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1000" t="inlineStr">
         <is>
@@ -87837,7 +87837,7 @@
         <v>45474</v>
       </c>
       <c r="E1001" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1001" t="inlineStr">
         <is>
@@ -87910,7 +87910,7 @@
         <v>45785</v>
       </c>
       <c r="E1002" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1002" t="inlineStr">
         <is>
@@ -87988,7 +87988,7 @@
         <v>45709</v>
       </c>
       <c r="E1003" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1003" t="inlineStr">
         <is>
@@ -88061,7 +88061,7 @@
         <v>45814</v>
       </c>
       <c r="E1004" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1004" t="inlineStr">
         <is>
@@ -88134,7 +88134,7 @@
         <v>45814</v>
       </c>
       <c r="E1005" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1005" t="inlineStr">
         <is>
@@ -88207,7 +88207,7 @@
         <v>45817</v>
       </c>
       <c r="E1006" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1006" t="inlineStr">
         <is>
@@ -88280,7 +88280,7 @@
         <v>45818</v>
       </c>
       <c r="E1007" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1007" t="inlineStr">
         <is>
@@ -88358,7 +88358,7 @@
         <v>45818</v>
       </c>
       <c r="E1008" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1008" t="inlineStr">
         <is>
@@ -88436,7 +88436,7 @@
         <v>45818</v>
       </c>
       <c r="E1009" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1009" t="inlineStr">
         <is>
@@ -88514,7 +88514,7 @@
         <v>45818</v>
       </c>
       <c r="E1010" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1010" t="inlineStr">
         <is>
@@ -88592,7 +88592,7 @@
         <v>45820</v>
       </c>
       <c r="E1011" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1011" t="inlineStr">
         <is>
@@ -88665,7 +88665,7 @@
         <v>45821</v>
       </c>
       <c r="E1012" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1012" t="inlineStr">
         <is>
@@ -88738,7 +88738,7 @@
         <v>45832</v>
       </c>
       <c r="E1013" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1013" t="inlineStr">
         <is>
@@ -88816,7 +88816,7 @@
         <v>45833</v>
       </c>
       <c r="E1014" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1014" t="inlineStr">
         <is>
@@ -88889,7 +88889,7 @@
         <v>45833</v>
       </c>
       <c r="E1015" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1015" t="inlineStr">
         <is>
@@ -88962,7 +88962,7 @@
         <v>45833</v>
       </c>
       <c r="E1016" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1016" t="inlineStr">
         <is>
@@ -89035,7 +89035,7 @@
         <v>45834</v>
       </c>
       <c r="E1017" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1017" t="inlineStr">
         <is>
@@ -89113,7 +89113,7 @@
         <v>45835</v>
       </c>
       <c r="E1018" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1018" t="inlineStr">
         <is>
@@ -89186,7 +89186,7 @@
         <v>45839</v>
       </c>
       <c r="E1019" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1019" t="inlineStr">
         <is>
@@ -89259,7 +89259,7 @@
         <v>45842</v>
       </c>
       <c r="E1020" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1020" t="inlineStr">
         <is>
@@ -89337,7 +89337,7 @@
         <v>45695</v>
       </c>
       <c r="E1021" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1021" t="inlineStr">
         <is>
@@ -89415,7 +89415,7 @@
         <v>45842</v>
       </c>
       <c r="E1022" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1022" t="inlineStr">
         <is>
@@ -89493,7 +89493,7 @@
         <v>45847</v>
       </c>
       <c r="E1023" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1023" t="inlineStr">
         <is>
@@ -89571,7 +89571,7 @@
         <v>45847</v>
       </c>
       <c r="E1024" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1024" t="inlineStr">
         <is>
@@ -89649,7 +89649,7 @@
         <v>45848</v>
       </c>
       <c r="E1025" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1025" t="inlineStr">
         <is>
@@ -89722,7 +89722,7 @@
         <v>45853</v>
       </c>
       <c r="E1026" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1026" t="inlineStr">
         <is>
@@ -89800,7 +89800,7 @@
         <v>45453</v>
       </c>
       <c r="E1027" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1027" t="inlineStr">
         <is>
@@ -89878,7 +89878,7 @@
         <v>45783</v>
       </c>
       <c r="E1028" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1028" t="inlineStr">
         <is>
@@ -89951,7 +89951,7 @@
         <v>45861</v>
       </c>
       <c r="E1029" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1029" t="inlineStr">
         <is>
@@ -90029,7 +90029,7 @@
         <v>45863</v>
       </c>
       <c r="E1030" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1030" t="inlineStr">
         <is>
@@ -90102,7 +90102,7 @@
         <v>45862</v>
       </c>
       <c r="E1031" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1031" t="inlineStr">
         <is>
@@ -90180,7 +90180,7 @@
         <v>45863</v>
       </c>
       <c r="E1032" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1032" t="inlineStr">
         <is>
@@ -90253,7 +90253,7 @@
         <v>45586</v>
       </c>
       <c r="E1033" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1033" t="inlineStr">
         <is>
@@ -90326,7 +90326,7 @@
         <v>45783</v>
       </c>
       <c r="E1034" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1034" t="inlineStr">
         <is>
@@ -90399,7 +90399,7 @@
         <v>45867</v>
       </c>
       <c r="E1035" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1035" t="inlineStr">
         <is>
@@ -90472,7 +90472,7 @@
         <v>45867</v>
       </c>
       <c r="E1036" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1036" t="inlineStr">
         <is>
@@ -90545,7 +90545,7 @@
         <v>44468</v>
       </c>
       <c r="E1037" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1037" t="inlineStr">
         <is>
@@ -90618,7 +90618,7 @@
         <v>45366</v>
       </c>
       <c r="E1038" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1038" t="inlineStr">
         <is>
@@ -90691,7 +90691,7 @@
         <v>45552</v>
       </c>
       <c r="E1039" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1039" t="inlineStr">
         <is>
@@ -90764,7 +90764,7 @@
         <v>45366</v>
       </c>
       <c r="E1040" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1040" t="inlineStr">
         <is>
@@ -90837,7 +90837,7 @@
         <v>45408</v>
       </c>
       <c r="E1041" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1041" t="inlineStr">
         <is>
@@ -90910,7 +90910,7 @@
         <v>45566</v>
       </c>
       <c r="E1042" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1042" t="inlineStr">
         <is>
@@ -90983,7 +90983,7 @@
         <v>45743</v>
       </c>
       <c r="E1043" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1043" t="inlineStr">
         <is>
@@ -91061,7 +91061,7 @@
         <v>45679</v>
       </c>
       <c r="E1044" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1044" t="inlineStr">
         <is>
@@ -91134,7 +91134,7 @@
         <v>46127</v>
       </c>
       <c r="E1045" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1045" t="inlineStr">
         <is>
@@ -91207,7 +91207,7 @@
         <v>46147</v>
       </c>
       <c r="E1046" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1046" t="inlineStr">
         <is>
@@ -91280,7 +91280,7 @@
         <v>46147</v>
       </c>
       <c r="E1047" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1047" t="inlineStr">
         <is>
@@ -91353,7 +91353,7 @@
         <v>46148</v>
       </c>
       <c r="E1048" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1048" t="inlineStr">
         <is>
@@ -91426,7 +91426,7 @@
         <v>46150</v>
       </c>
       <c r="E1049" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1049" t="inlineStr">
         <is>
@@ -91499,7 +91499,7 @@
         <v>46150</v>
       </c>
       <c r="E1050" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1050" t="inlineStr">
         <is>
